--- a/Result/profitability/6164.xlsx
+++ b/Result/profitability/6164.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04250000000000001</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>33.005</v>
+        <v>33.16375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.31</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.07875000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>32.59875</v>
+        <v>32.26875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09875</v>
+        <v>0.1</v>
       </c>
       <c r="N4" t="n">
-        <v>31.95625</v>
+        <v>31.815</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.12875</v>
+        <v>0.15875</v>
       </c>
       <c r="N5" t="n">
-        <v>32.59625</v>
+        <v>31.84125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.15875</v>
+        <v>0.16625</v>
       </c>
       <c r="N6" t="n">
-        <v>31.57625</v>
+        <v>32.10375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>0.18</v>
+        <v>0.1875</v>
       </c>
       <c r="N7" t="n">
-        <v>32.73375</v>
+        <v>32.915</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.205</v>
+        <v>0.2125</v>
       </c>
       <c r="N8" t="n">
-        <v>33.39375</v>
+        <v>33.755</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.2675</v>
       </c>
       <c r="N10" t="n">
-        <v>34.6975</v>
+        <v>34.69750000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.2925</v>
       </c>
       <c r="N11" t="n">
-        <v>35.72750000000001</v>
+        <v>35.7275</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6164</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>215</v>
+      </c>
+      <c r="D75" t="n">
+        <v>143</v>
+      </c>
+      <c r="E75" t="n">
+        <v>71</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04500000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.1675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.890000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09544253632760902</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.846153846153846</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.039999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1540423361387401</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
